--- a/questionnaire_templates/006_principles_of_management_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/006_principles_of_management_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>manager_leadership_style</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Manager Leadership Style</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,46 +538,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>management_style</t>
+          <t>leadership_skills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>management_style</t>
+          <t>Leadership Skills</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>leadership_skills</t>
+          <t>conflict_management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leadership_skills</t>
+          <t>Conflict Management</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>communication_skills</t>
+          <t>communication_strategy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>communication_skills</t>
+          <t>Communication Strategy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>Time Management</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>goal_setting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>goal_setting</t>
+          <t>decision_making</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>goal_setting</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,23 +676,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>decision_making</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>decision_making</t>
+          <t>Problem Solving</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>problem_solving</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>problem_solving</t>
+          <t>Adaptability</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>situational_awareness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>Situational Awareness</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>situational_awareness</t>
+          <t>emotional_intelligence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>situational_awareness</t>
+          <t>Emotional Intelligence</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emotional_intelligence</t>
+          <t>situational_priorities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>emotional_intelligence</t>
+          <t>Situational Priorities</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>situational_situational</t>
+          <t>situational_analysis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>situational</t>
+          <t>Situational Analysis</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>situational_situational</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>situational</t>
+          <t>Conflict Resolution</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,248 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>situational_situational</t>
+          <t>situational_management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>situational</t>
+          <t>Situational Management</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>situational_situational</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>situational</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +896,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>management_style_choices</t>
+          <t>manager_leadership_style_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>autocratic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>autocratic</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>management_style_choices</t>
+          <t>manager_leadership_style_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>participative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>participative</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>management_style_choices</t>
+          <t>manager_leadership_style_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>laissez-faire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>laissez-faire</t>
         </is>
       </c>
     </row>
@@ -1182,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>effective_communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>effective communication</t>
         </is>
       </c>
     </row>
@@ -1199,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>problem solving</t>
         </is>
       </c>
     </row>
@@ -1216,114 +986,114 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>adaptability</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>communication_skills_choices</t>
+          <t>conflict_management_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>avoid_conflict</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>avoid conflict</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>communication_skills_choices</t>
+          <t>conflict_management_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>face_conflict</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>face conflict</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>communication_skills_choices</t>
+          <t>conflict_management_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>seek_mediation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>seek mediation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>communication_strategy_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>verbal_communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>verbal communication</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>communication_strategy_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>nonverbal_communication</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>nonverbal communication</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>communication_strategy_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>listening_skills</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>listening skills</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>smart_goals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>smart goals</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>goal_oriented</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>goal oriented</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>goal_set</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>goal set</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>data_driven</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>data driven</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>intuitive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>intuitive</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>consensus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>consensus</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>analyze</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>analyze</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>deduce</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>deduce</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>improve</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>improve</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>quickly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>quickly</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>slowly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>slowly</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>self_awareness</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>self awareness</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>self_regulation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>self regulation</t>
         </is>
       </c>
     </row>
@@ -1624,573 +1394,216 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>motivation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_priorities_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_priorities_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_priorities_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_analysis_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>in_depth</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>in depth</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_analysis_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>wide</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>wide</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_analysis_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>shallow</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>shallow</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>conflict_resolution_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>conflict_avoidance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>conflict avoidance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>conflict_resolution_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>conflict resolution</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>conflict_resolution_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>seek_help</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>seek help</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_management_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_management_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>situational_situational_choices</t>
+          <t>situational_management_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>situational_situational_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>low</t>
         </is>
       </c>
     </row>
